--- a/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_Evidence" sheetId="1" r:id="Rac07150f58f348cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_INDEX" sheetId="2" r:id="Rf63b12dd8e44411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="3" r:id="R58b7e5ec06b6490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入力フロー" sheetId="4" r:id="R2f8a45b38b8f46e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_取替方式" sheetId="5" r:id="R2cc6442cbebe4e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_仕様区分" sheetId="6" r:id="Re9cd1ea39a0740cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_窓種" sheetId="7" r:id="R9e37b3c838d34538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_枠仕様" sheetId="8" r:id="R1c7ebb3968fd44e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03B_窓種枠設定" sheetId="9" r:id="R8dad125fb079457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_窓種固有仕様" sheetId="10" r:id="R778d6b1905114f63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_サイズルール" sheetId="11" r:id="Rc7adedc598774628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_サイズ区間" sheetId="12" r:id="Rf65897a061ab462c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05B_境界ルール" sheetId="13" r:id="R5dba2755264f4409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_色" sheetId="14" r:id="R9361dc5740b247dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_色適用条件" sheetId="15" r:id="R302d9d895ea544aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_網戸" sheetId="16" r:id="Rc6cabc6171f14965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_網戸適用条件" sheetId="17" r:id="Rbc392b46a05e4f60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ガラス" sheetId="18" r:id="Re2bc13b471ee457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08A_ガラス適用条件" sheetId="19" r:id="R2873978209d142b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_その他OP" sheetId="20" r:id="Ra780156d91104aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09A_OP依存関係" sheetId="21" r:id="R0b8cbf1c8dfa4b56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_適用条件" sheetId="22" r:id="Re46d59de40b04c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10A_既設窓互換" sheetId="23" r:id="R6588484243f64800"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10B_現調項目" sheetId="24" r:id="R061867918c95455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_QA" sheetId="25" r:id="R8538704b246144af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_開口構成" sheetId="26" r:id="Rdbb1cd7b10964845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_見積入力テスト" sheetId="27" r:id="Rd369a940619448ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C_化粧カバー見付" sheetId="28" r:id="Rcf55141d95cb4bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_共通参照" sheetId="29" r:id="R37befb22483a42fd"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="90_Evidence" sheetId="1" r:id="Rac07150f58f348cf"/>
+    <sheet name="00_INDEX" sheetId="2" r:id="Rf63b12dd8e44411c"/>
+    <sheet name="00_README" sheetId="3" r:id="R58b7e5ec06b6490b"/>
+    <sheet name="01_入力フロー" sheetId="4" r:id="R2f8a45b38b8f46e6"/>
+    <sheet name="02_取替方式" sheetId="5" r:id="R2cc6442cbebe4e60"/>
+    <sheet name="02A_仕様区分" sheetId="6" r:id="Re9cd1ea39a0740cc"/>
+    <sheet name="03_窓種" sheetId="7" r:id="R9e37b3c838d34538"/>
+    <sheet name="03A_枠仕様" sheetId="8" r:id="R1c7ebb3968fd44e7"/>
+    <sheet name="03B_窓種枠設定" sheetId="9" r:id="R8dad125fb079457e"/>
+    <sheet name="04_窓種固有仕様" sheetId="10" r:id="R778d6b1905114f63"/>
+    <sheet name="05_サイズルール" sheetId="11" r:id="Rc7adedc598774628"/>
+    <sheet name="05A_サイズ区間" sheetId="12" r:id="Rf65897a061ab462c"/>
+    <sheet name="05B_境界ルール" sheetId="13" r:id="R5dba2755264f4409"/>
+    <sheet name="06_色" sheetId="14" r:id="R9361dc5740b247dd"/>
+    <sheet name="06A_色適用条件" sheetId="15" r:id="R302d9d895ea544aa"/>
+    <sheet name="07_網戸" sheetId="16" r:id="Rc6cabc6171f14965"/>
+    <sheet name="07A_網戸適用条件" sheetId="17" r:id="Rbc392b46a05e4f60"/>
+    <sheet name="08_ガラス" sheetId="18" r:id="Re2bc13b471ee457f"/>
+    <sheet name="08A_ガラス適用条件" sheetId="19" r:id="R2873978209d142b2"/>
+    <sheet name="09_その他OP" sheetId="20" r:id="Ra780156d91104aa6"/>
+    <sheet name="09A_OP依存関係" sheetId="21" r:id="R0b8cbf1c8dfa4b56"/>
+    <sheet name="10_適用条件" sheetId="22" r:id="Re46d59de40b04c3b"/>
+    <sheet name="10A_既設窓互換" sheetId="23" r:id="R6588484243f64800"/>
+    <sheet name="10B_現調項目" sheetId="24" r:id="R061867918c95455f"/>
+    <sheet name="99_QA" sheetId="25" r:id="R8538704b246144af"/>
+    <sheet name="04A_開口構成" sheetId="26" r:id="Rdbb1cd7b10964845"/>
+    <sheet name="11_見積入力テスト" sheetId="27" r:id="Rd369a940619448ff"/>
+    <sheet name="10C_化粧カバー見付" sheetId="28" r:id="Rcf55141d95cb4bf6"/>
+    <sheet name="12_共通参照" sheetId="29" r:id="R37befb22483a42fd"/>
+    <sheet name="14_UI選択契約" sheetId="30" r:id="rIdReplusUiV9"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1264,6 +1265,643 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/replus-ui-v9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="184">
+        <v>リプラス住宅用・共通UI選択契約</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="181">
+        <v>分類</v>
+      </c>
+      <c r="B2" t="str" s="182">
+        <v>対象</v>
+      </c>
+      <c r="C2" t="str" s="182">
+        <v>依存元</v>
+      </c>
+      <c r="D2" t="str" s="182">
+        <v>処理</v>
+      </c>
+      <c r="E2" t="str" s="183">
+        <v>根拠区分</v>
+      </c>
+      <c r="F2" t="str">
+        <v>revision</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="184">
+        <v>色連動</v>
+      </c>
+      <c r="B3" t="str" s="185">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C3" t="str" s="185">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D3" t="str" s="185">
+        <v>{"targetField": "exterior_cover_color", "parents": ["sash_exterior_color"], "cases": [{"when": {"sash_exterior_color": "T"}, "value": "T"}, {"when": {"sash_exterior_color": "G"}, "value": "G"}, {"when": {"sash_exterior_color": "K"}, "value": "K"}, {"when": {"sash_exterior_color": "D"}, "value": "D"}, {"when": {"sash_exterior_color": "W"}, "value": "W"}], "resolvedMessage": "本体外観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E3" t="str" s="186">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F3" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="184">
+        <v>色連動</v>
+      </c>
+      <c r="B4" t="str" s="185">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C4" t="str" s="185">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D4" t="str" s="185">
+        <v>{"targetField": "interior_cover_color", "parents": ["sash_interior_color"], "cases": [{"when": {"sash_interior_color": "M"}, "value": "M"}, {"when": {"sash_interior_color": "C"}, "value": "C"}, {"when": {"sash_interior_color": "B"}, "value": "B"}, {"when": {"sash_interior_color": "P"}, "value": "P"}, {"when": {"sash_interior_color": "F"}, "value": "F"}], "resolvedMessage": "本体内観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E4" t="str" s="186">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F4" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B5" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="C5" t="str" s="185"/>
+      <c r="D5" t="str" s="185">
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E5" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F5" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B6" t="str" s="185">
+        <v>frame_type</v>
+      </c>
+      <c r="C6" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D6" t="str" s="185">
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E6" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F6" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B7" t="str" s="185">
+        <v>spec_panel_configuration</v>
+      </c>
+      <c r="C7" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D7" t="str" s="185">
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E7" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F7" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B8" t="str" s="185">
+        <v>spec_height_category</v>
+      </c>
+      <c r="C8" t="str" s="185">
+        <v>window_type,custom_width,custom_height</v>
+      </c>
+      <c r="D8" t="str" s="185">
+        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
+      </c>
+      <c r="E8" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F8" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B9" t="str" s="185">
+        <v>spec_sash_configuration</v>
+      </c>
+      <c r="C9" t="str" s="185">
+        <v>spec_height_category,spec_panel_configuration,window_type</v>
+      </c>
+      <c r="D9" t="str" s="185">
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E9" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F9" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B10" t="str" s="185">
+        <v>screen</v>
+      </c>
+      <c r="C10" t="str" s="185">
+        <v>spec_height_category,window_type</v>
+      </c>
+      <c r="D10" t="str" s="185">
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+      </c>
+      <c r="E10" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F10" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>size_mode</v>
+      </c>
+      <c r="C11" t="str" s="185"/>
+      <c r="D11" t="str" s="185">
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F11" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>custom_width</v>
+      </c>
+      <c r="C12" t="str" s="185">
+        <v>size_mode</v>
+      </c>
+      <c r="D12" t="str" s="185">
+        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F12" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B13" t="str" s="185">
+        <v>custom_height</v>
+      </c>
+      <c r="C13" t="str" s="185">
+        <v>size_mode</v>
+      </c>
+      <c r="D13" t="str" s="185">
+        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E13" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F13" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="C14" t="str" s="185"/>
+      <c r="D14" t="str" s="185">
+        <v>{"label": "本体外観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F14" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C15" t="str" s="185">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D15" t="str" s="185">
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F15" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B16" t="str" s="185">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="C16" t="str" s="185"/>
+      <c r="D16" t="str" s="185">
+        <v>{"label": "本体内観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E16" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F16" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B17" t="str" s="185">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C17" t="str" s="185">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D17" t="str" s="185">
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E17" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F17" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B18" t="str" s="185">
+        <v>wooden_casing_color</v>
+      </c>
+      <c r="C18" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="D18" t="str" s="185">
+        <v>{"label": "木製ケーシング色", "group": "part_detail", "internal": false}</v>
+      </c>
+      <c r="E18" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F18" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B19" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="C19" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D19" t="str" s="185">
+        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
+      </c>
+      <c r="E19" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F19" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B20" t="str" s="185">
+        <v>usage_humidity</v>
+      </c>
+      <c r="C20" t="str" s="185"/>
+      <c r="D20" t="str" s="185">
+        <v>{"label": "使用環境", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E20" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F20" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B21" t="str" s="185">
+        <v>installation_method</v>
+      </c>
+      <c r="C21" t="str" s="185"/>
+      <c r="D21" t="str" s="185">
+        <v>{"label": "施工方法", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E21" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F21" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B22" t="str" s="185">
+        <v>installation_region</v>
+      </c>
+      <c r="C22" t="str" s="185"/>
+      <c r="D22" t="str" s="185">
+        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E22" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F22" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B23" t="str" s="185">
+        <v>glass_category</v>
+      </c>
+      <c r="C23" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D23" t="str" s="185">
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E23" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F23" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B24" t="str" s="185">
+        <v>glass</v>
+      </c>
+      <c r="C24" t="str" s="185">
+        <v>glass_category,installation_region,window_type</v>
+      </c>
+      <c r="D24" t="str" s="185">
+        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E24" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F24" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B25" t="str" s="185">
+        <v>glass_gas</v>
+      </c>
+      <c r="C25" t="str" s="185">
+        <v>glass_category,window_type</v>
+      </c>
+      <c r="D25" t="str" s="185">
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E25" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F25" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B26" t="str" s="185">
+        <v>glass_spacer</v>
+      </c>
+      <c r="C26" t="str" s="185">
+        <v>glass_category,glass_gas,window_type</v>
+      </c>
+      <c r="D26" t="str" s="185">
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E26" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F26" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B27" t="str" s="185">
+        <v>glass_function</v>
+      </c>
+      <c r="C27" t="str" s="185">
+        <v>glass_category,glass,window_type</v>
+      </c>
+      <c r="D27" t="str" s="185">
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E27" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F27" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B28" t="str" s="185">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C28" t="str" s="185">
+        <v>glass,glass_function</v>
+      </c>
+      <c r="D28" t="str" s="185">
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E28" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F28" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B29" t="str" s="185">
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C29" t="str" s="185"/>
+      <c r="D29" t="str" s="185">
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E29" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F29" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B30" t="str" s="185">
+        <v>exterior_cover_type</v>
+      </c>
+      <c r="C30" t="str" s="185">
+        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+      </c>
+      <c r="D30" t="str" s="185">
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E30" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F30" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B31" t="str" s="185">
+        <v>survey_cover_top</v>
+      </c>
+      <c r="C31" t="str" s="185"/>
+      <c r="D31" t="str" s="185">
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E31" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F31" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B32" t="str" s="185">
+        <v>survey_cover_bottom</v>
+      </c>
+      <c r="C32" t="str" s="185"/>
+      <c r="D32" t="str" s="185">
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E32" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F32" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B33" t="str" s="185">
+        <v>survey_cover_side</v>
+      </c>
+      <c r="C33" t="str" s="185"/>
+      <c r="D33" t="str" s="185">
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E33" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F33" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10249,371 +10887,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="178" t="str">
-        <x:v>01_入力フロー｜TWタイプ</x:v>
-      </x:c>
-      <x:c r="B1" s="178"/>
-      <x:c r="C1" s="178"/>
-      <x:c r="D1" s="178"/>
-      <x:c r="E1" s="178"/>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="181" t="str">
-        <x:v>順序</x:v>
-      </x:c>
-      <x:c r="B3" s="182" t="str">
-        <x:v>表示項目</x:v>
-      </x:c>
-      <x:c r="C3" s="182" t="str">
-        <x:v>データキー</x:v>
-      </x:c>
-      <x:c r="D3" s="182" t="str">
-        <x:v>候補/入力</x:v>
-      </x:c>
-      <x:c r="E3" s="183" t="str">
-        <x:v>制御</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="184" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="185" t="str">
-        <x:v>取替方式</x:v>
-      </x:c>
-      <x:c r="C4" s="185" t="str">
-        <x:v>installation_system_id</x:v>
-      </x:c>
-      <x:c r="D4" s="185" t="str">
-        <x:v>RPL_DIRECT</x:v>
-      </x:c>
-      <x:c r="E4" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="184" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="185" t="str">
-        <x:v>仕様区分</x:v>
-      </x:c>
-      <x:c r="C5" s="185" t="str">
-        <x:v>variation_id</x:v>
-      </x:c>
-      <x:c r="D5" s="185" t="str">
-        <x:v>RPL_TW</x:v>
-      </x:c>
-      <x:c r="E5" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="184" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="185" t="str">
-        <x:v>開口構成</x:v>
-      </x:c>
-      <x:c r="C6" s="185" t="str">
-        <x:v>opening_configuration</x:v>
-      </x:c>
-      <x:c r="D6" s="185" t="str">
-        <x:v>SINGLE</x:v>
-      </x:c>
-      <x:c r="E6" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="184" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="185" t="str">
-        <x:v>窓種</x:v>
-      </x:c>
-      <x:c r="C7" s="185" t="str">
-        <x:v>window_type_id</x:v>
-      </x:c>
-      <x:c r="D7" s="185" t="str">
-        <x:v>RPL_TW_SLD / 引違い窓</x:v>
-      </x:c>
-      <x:c r="E7" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="184" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="185" t="str">
-        <x:v>建数</x:v>
-      </x:c>
-      <x:c r="C8" s="185" t="str">
-        <x:v>panel_configuration</x:v>
-      </x:c>
-      <x:c r="D8" s="185" t="str">
-        <x:v>2枚建 / 4枚建</x:v>
-      </x:c>
-      <x:c r="E8" s="186" t="str">
-        <x:v>動的選択</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="184" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="185" t="str">
-        <x:v>高さ区分</x:v>
-      </x:c>
-      <x:c r="C9" s="185" t="str">
-        <x:v>height_category</x:v>
-      </x:c>
-      <x:c r="D9" s="185" t="str">
-        <x:v>マド / テラス</x:v>
-      </x:c>
-      <x:c r="E9" s="186" t="str">
-        <x:v>動的選択</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="184" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="185" t="str">
-        <x:v>障子仕様</x:v>
-      </x:c>
-      <x:c r="C10" s="185" t="str">
-        <x:v>sash_configuration</x:v>
-      </x:c>
-      <x:c r="D10" s="185" t="str">
-        <x:v>TG / 把手 / 大壁和室用</x:v>
-      </x:c>
-      <x:c r="E10" s="186" t="str">
-        <x:v>建数・高さ区分で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="184" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="185" t="str">
-        <x:v>採寸W/H</x:v>
-      </x:c>
-      <x:c r="C11" s="185" t="str">
-        <x:v>survey_w / survey_h</x:v>
-      </x:c>
-      <x:c r="D11" s="185" t="str">
-        <x:v>現場入力</x:v>
-      </x:c>
-      <x:c r="E11" s="186" t="str">
-        <x:v>3点採寸は現調レイヤー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="184" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="185" t="str">
-        <x:v>出来寸W/H</x:v>
-      </x:c>
-      <x:c r="C12" s="185" t="str">
-        <x:v>finished_w / finished_h</x:v>
-      </x:c>
-      <x:c r="D12" s="185" t="str">
-        <x:v>自動算出</x:v>
-      </x:c>
-      <x:c r="E12" s="186" t="str">
-        <x:v>WD=WS-10 / HD=HS-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="184" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="185" t="str">
-        <x:v>外観色</x:v>
-      </x:c>
-      <x:c r="C13" s="185" t="str">
-        <x:v>sash_exterior_color</x:v>
-      </x:c>
-      <x:c r="D13" s="185" t="str">
-        <x:v>5色</x:v>
-      </x:c>
-      <x:c r="E13" s="186" t="str">
-        <x:v>TWタイプ公式色のみ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="184" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="185" t="str">
-        <x:v>内観色</x:v>
-      </x:c>
-      <x:c r="C14" s="185" t="str">
-        <x:v>sash_interior_color</x:v>
-      </x:c>
-      <x:c r="D14" s="185" t="str">
-        <x:v>5色</x:v>
-      </x:c>
-      <x:c r="E14" s="186" t="str">
-        <x:v>外観との組合せ自由</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="184" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="185" t="str">
-        <x:v>網戸</x:v>
-      </x:c>
-      <x:c r="C15" s="185" t="str">
-        <x:v>screen_configuration</x:v>
-      </x:c>
-      <x:c r="D15" s="185" t="str">
-        <x:v>なし/中桟無/中桟付</x:v>
-      </x:c>
-      <x:c r="E15" s="186" t="str">
-        <x:v>中桟付はHD条件</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="184" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="185" t="str">
-        <x:v>ネット</x:v>
-      </x:c>
-      <x:c r="C16" s="185" t="str">
-        <x:v>screen_mesh</x:v>
-      </x:c>
-      <x:c r="D16" s="185" t="str">
-        <x:v>標準/きれい/虫イヤ/ペット</x:v>
-      </x:c>
-      <x:c r="E16" s="186" t="str">
-        <x:v>網戸あり時のみ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="184" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" s="185" t="str">
-        <x:v>ガラス</x:v>
-      </x:c>
-      <x:c r="C17" s="185" t="str">
-        <x:v>glass_category</x:v>
-      </x:c>
-      <x:c r="D17" s="185" t="str">
-        <x:v>専用Low-Eトリプル</x:v>
-      </x:c>
-      <x:c r="E17" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="184" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B18" s="185" t="str">
-        <x:v>Low-E構成</x:v>
-      </x:c>
-      <x:c r="C18" s="185" t="str">
-        <x:v>glass_low_e_color</x:v>
-      </x:c>
-      <x:c r="D18" s="185" t="str">
-        <x:v>公式構成</x:v>
-      </x:c>
-      <x:c r="E18" s="186" t="str">
-        <x:v>地域/要確認条件で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="184" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B19" s="185" t="str">
-        <x:v>ガス</x:v>
-      </x:c>
-      <x:c r="C19" s="185" t="str">
-        <x:v>gas_type</x:v>
-      </x:c>
-      <x:c r="D19" s="185" t="str">
-        <x:v>アルゴン / クリプトン</x:v>
-      </x:c>
-      <x:c r="E19" s="186" t="str">
-        <x:v>選択</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="184" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B20" s="185" t="str">
-        <x:v>ガラス仕上げ</x:v>
-      </x:c>
-      <x:c r="C20" s="185" t="str">
-        <x:v>glass_pattern/function</x:v>
-      </x:c>
-      <x:c r="D20" s="185" t="str">
-        <x:v>透明/型/フロスト/安全合わせ等</x:v>
-      </x:c>
-      <x:c r="E20" s="186" t="str">
-        <x:v>公式設定で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="184" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B21" s="185" t="str">
-        <x:v>オプション</x:v>
-      </x:c>
-      <x:c r="C21" s="185" t="str">
-        <x:v>option_id</x:v>
-      </x:c>
-      <x:c r="D21" s="185" t="str">
-        <x:v>主要有償品</x:v>
-      </x:c>
-      <x:c r="E21" s="186" t="str">
-        <x:v>依存関係適用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="187" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B22" s="188" t="str">
-        <x:v>現調/施工判定</x:v>
-      </x:c>
-      <x:c r="C22" s="188" t="str">
-        <x:v>survey/installation_condition</x:v>
-      </x:c>
-      <x:c r="D22" s="188" t="str">
-        <x:v>別UI</x:v>
-      </x:c>
-      <x:c r="E22" s="189" t="str">
-        <x:v>商品選択とは分離</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="62" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" t="str" s="178">
+        <v>リプラス住宅用・グローバルセレクションフロー</v>
+      </c>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="str" s="181">
+        <v>順番</v>
+      </c>
+      <c r="B3" t="str" s="182">
+        <v>表示項目</v>
+      </c>
+      <c r="C3" t="str" s="182">
+        <v>データキー</v>
+      </c>
+      <c r="D3" t="str" s="182">
+        <v>候補/入力</v>
+      </c>
+      <c r="E3" t="str" s="183">
+        <v>制御方針</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="184">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="185">
+        <v>商品・リプラス仕様</v>
+      </c>
+      <c r="C4" t="str" s="185">
+        <v>product / specification</v>
+      </c>
+      <c r="D4" t="str" s="185">
+        <v>リプラス住宅用 → 仕様</v>
+      </c>
+      <c r="E4" t="str" s="186">
+        <v>今回承認されたアプリ運用ルール</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="184">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str" s="185">
+        <v>設置・施工条件</v>
+      </c>
+      <c r="C5" t="str" s="185">
+        <v>context</v>
+      </c>
+      <c r="D5" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E5" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="184">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str" s="185">
+        <v>窓種・基本仕様</v>
+      </c>
+      <c r="C6" t="str" s="185">
+        <v>opening</v>
+      </c>
+      <c r="D6" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E6" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="184">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str" s="185">
+        <v>本体色</v>
+      </c>
+      <c r="C7" t="str" s="185">
+        <v>finish</v>
+      </c>
+      <c r="D7" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E7" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="184">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str" s="185">
+        <v>網戸</v>
+      </c>
+      <c r="C8" t="str" s="185">
+        <v>screen</v>
+      </c>
+      <c r="D8" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E8" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="184">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str" s="185">
+        <v>ガラス</v>
+      </c>
+      <c r="C9" t="str" s="185">
+        <v>glazing</v>
+      </c>
+      <c r="D9" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E9" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="184">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str" s="185">
+        <v>室内側の仕上げ・アングルカバー</v>
+      </c>
+      <c r="C10" t="str" s="185">
+        <v>interior_finish</v>
+      </c>
+      <c r="D10" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E10" t="str" s="186">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="184">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>室外側の仕上げ・化粧カバー</v>
+      </c>
+      <c r="C11" t="str" s="185">
+        <v>exterior_finish</v>
+      </c>
+      <c r="D11" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="184">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>新設サッシのオプション</v>
+      </c>
+      <c r="C12" t="str" s="185">
+        <v>native_options</v>
+      </c>
+      <c r="D12" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="184">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str" s="185">
+        <v>追加部材・オプション</v>
+      </c>
+      <c r="C13" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="D13" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E13" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="184">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>選択した部材の仕様</v>
+      </c>
+      <c r="C14" t="str" s="185">
+        <v>part_detail</v>
+      </c>
+      <c r="D14" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="184">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C15" t="str" s="185">
+        <v>survey</v>
+      </c>
+      <c r="D15" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="184">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str" s="185">
+        <v>製品寸法</v>
+      </c>
+      <c r="C16" t="str" s="185">
+        <v>size</v>
+      </c>
+      <c r="D16" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E16" t="str" s="186">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="184"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="186"/>
+      <c r="F17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="184"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="186"/>
+      <c r="F18"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="184"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="186"/>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="184"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="186"/>
+      <c r="F20"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="184"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="186"/>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="187"/>
+      <c r="B22" s="188"/>
+      <c r="C22" s="188"/>
+      <c r="D22" s="188"/>
+      <c r="E22" s="189"/>
+      <c r="F22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
@@ -1316,7 +1316,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1336,7 +1336,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1354,7 +1354,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1374,7 +1374,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1394,7 +1394,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1414,7 +1414,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1434,7 +1434,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1454,7 +1454,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1472,7 +1472,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1492,7 +1492,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1512,7 +1512,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1530,7 +1530,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1550,7 +1550,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1568,7 +1568,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1588,7 +1588,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1608,7 +1608,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1628,7 +1628,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1640,13 +1640,13 @@
       </c>
       <c r="C20" t="str" s="185"/>
       <c r="D20" t="str" s="185">
-        <v>{"label": "使用環境", "group": "context", "internal": false}</v>
+        <v>{"label": "使用環境", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E20" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1664,7 +1664,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1702,7 +1702,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1722,7 +1722,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1742,7 +1742,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1762,7 +1762,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1782,7 +1782,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1802,7 +1802,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1820,7 +1820,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1840,7 +1840,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1852,13 +1852,13 @@
       </c>
       <c r="C31" t="str" s="185"/>
       <c r="D31" t="str" s="185">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E31" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1870,13 +1870,13 @@
       </c>
       <c r="C32" t="str" s="185"/>
       <c r="D32" t="str" s="185">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E32" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1888,13 +1888,13 @@
       </c>
       <c r="C33" t="str" s="185"/>
       <c r="D33" t="str" s="185">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E33" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -11082,10 +11082,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="185">
-        <v>新設サッシのオプション</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C12" t="str" s="185">
-        <v>native_options</v>
+        <v>options</v>
       </c>
       <c r="D12" t="str" s="185">
         <v>選択・確認</v>
@@ -11100,10 +11100,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="185">
-        <v>追加部材・オプション</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C13" t="str" s="185">
-        <v>options</v>
+        <v>part_detail</v>
       </c>
       <c r="D13" t="str" s="185">
         <v>選択・確認</v>
@@ -11118,53 +11118,33 @@
         <v>11</v>
       </c>
       <c r="B14" t="str" s="185">
-        <v>選択した部材の仕様</v>
+        <v>製品寸法</v>
       </c>
       <c r="C14" t="str" s="185">
-        <v>part_detail</v>
+        <v>size</v>
       </c>
       <c r="D14" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E14" t="str" s="186">
-        <v>対応する項目のみ表示</v>
+        <v>採寸後に再評価</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n" s="184">
-        <v>12</v>
-      </c>
-      <c r="B15" t="str" s="185">
-        <v>現場採寸・取付条件</v>
-      </c>
-      <c r="C15" t="str" s="185">
-        <v>survey</v>
-      </c>
-      <c r="D15" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E15" t="str" s="186">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A15" s="184"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="186"/>
       <c r="F15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n" s="184">
-        <v>13</v>
-      </c>
-      <c r="B16" t="str" s="185">
-        <v>製品寸法</v>
-      </c>
-      <c r="C16" t="str" s="185">
-        <v>size</v>
-      </c>
-      <c r="D16" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E16" t="str" s="186">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="186"/>
       <c r="F16"/>
     </row>
     <row r="17">

--- a/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
@@ -1301,7 +1301,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str" s="184">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B3" t="str" s="185">
         <v>exterior_cover_color</v>
@@ -1316,12 +1316,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="184">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B4" t="str" s="185">
         <v>interior_cover_color</v>
@@ -1336,45 +1336,45 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str" s="184">
-        <v>フロー</v>
+        <v>NUMERIC_INPUT_PAIRS</v>
       </c>
       <c r="B5" t="str" s="185">
-        <v>window_type</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C5" t="str" s="185"/>
       <c r="D5" t="str" s="185">
-        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+        <v>{"basisField": "dimension_basis", "measuredBasis": "SURVEY", "finishedBasis": "FINISHED", "legacyBasis": "FINISHED", "evaluationAssignments": {"size_mode": "CUSTOM"}, "pairs": [{"measuredField": "survey_width", "finishedField": "custom_width", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}, {"measuredField": "survey_height", "finishedField": "custom_height", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}]}</v>
       </c>
       <c r="E5" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str" s="184">
-        <v>フロー</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B6" t="str" s="185">
-        <v>frame_type</v>
+        <v>inner_fit_required_component</v>
       </c>
       <c r="C6" t="str" s="185">
-        <v>window_type</v>
+        <v>installation_method</v>
       </c>
       <c r="D6" t="str" s="185">
-        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "TW-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "TW-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
       </c>
       <c r="E6" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1382,19 +1382,17 @@
         <v>フロー</v>
       </c>
       <c r="B7" t="str" s="185">
-        <v>spec_panel_configuration</v>
-      </c>
-      <c r="C7" t="str" s="185">
         <v>window_type</v>
       </c>
+      <c r="C7" t="str" s="185"/>
       <c r="D7" t="str" s="185">
-        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
       </c>
       <c r="E7" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1402,19 +1400,19 @@
         <v>フロー</v>
       </c>
       <c r="B8" t="str" s="185">
-        <v>spec_height_category</v>
+        <v>frame_type</v>
       </c>
       <c r="C8" t="str" s="185">
-        <v>window_type,custom_width,custom_height</v>
+        <v>window_type</v>
       </c>
       <c r="D8" t="str" s="185">
-        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E8" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1422,19 +1420,19 @@
         <v>フロー</v>
       </c>
       <c r="B9" t="str" s="185">
-        <v>spec_sash_configuration</v>
+        <v>spec_panel_configuration</v>
       </c>
       <c r="C9" t="str" s="185">
-        <v>spec_height_category,spec_panel_configuration,window_type</v>
+        <v>window_type</v>
       </c>
       <c r="D9" t="str" s="185">
-        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
       </c>
       <c r="E9" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1442,19 +1440,19 @@
         <v>フロー</v>
       </c>
       <c r="B10" t="str" s="185">
-        <v>screen</v>
+        <v>spec_height_category</v>
       </c>
       <c r="C10" t="str" s="185">
-        <v>spec_height_category,window_type</v>
+        <v>window_type,custom_width,custom_height</v>
       </c>
       <c r="D10" t="str" s="185">
-        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
       </c>
       <c r="E10" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1462,17 +1460,19 @@
         <v>フロー</v>
       </c>
       <c r="B11" t="str" s="185">
-        <v>size_mode</v>
-      </c>
-      <c r="C11" t="str" s="185"/>
+        <v>spec_sash_configuration</v>
+      </c>
+      <c r="C11" t="str" s="185">
+        <v>spec_height_category,spec_panel_configuration,window_type</v>
+      </c>
       <c r="D11" t="str" s="185">
-        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E11" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1480,19 +1480,19 @@
         <v>フロー</v>
       </c>
       <c r="B12" t="str" s="185">
-        <v>custom_width</v>
+        <v>screen</v>
       </c>
       <c r="C12" t="str" s="185">
-        <v>size_mode</v>
+        <v>spec_height_category,window_type</v>
       </c>
       <c r="D12" t="str" s="185">
-        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
       </c>
       <c r="E12" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1500,19 +1500,17 @@
         <v>フロー</v>
       </c>
       <c r="B13" t="str" s="185">
-        <v>custom_height</v>
-      </c>
-      <c r="C13" t="str" s="185">
         <v>size_mode</v>
       </c>
+      <c r="C13" t="str" s="185"/>
       <c r="D13" t="str" s="185">
-        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": true}</v>
       </c>
       <c r="E13" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1530,7 +1528,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1550,7 +1548,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1568,7 +1566,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1588,7 +1586,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1608,7 +1606,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1628,7 +1626,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1636,17 +1634,17 @@
         <v>フロー</v>
       </c>
       <c r="B20" t="str" s="185">
-        <v>usage_humidity</v>
+        <v>installation_region</v>
       </c>
       <c r="C20" t="str" s="185"/>
       <c r="D20" t="str" s="185">
-        <v>{"label": "使用環境", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
       </c>
       <c r="E20" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1654,17 +1652,19 @@
         <v>フロー</v>
       </c>
       <c r="B21" t="str" s="185">
-        <v>installation_method</v>
-      </c>
-      <c r="C21" t="str" s="185"/>
+        <v>glass_category</v>
+      </c>
+      <c r="C21" t="str" s="185">
+        <v>window_type</v>
+      </c>
       <c r="D21" t="str" s="185">
-        <v>{"label": "施工方法", "group": "context", "internal": false}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E21" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1672,17 +1672,19 @@
         <v>フロー</v>
       </c>
       <c r="B22" t="str" s="185">
-        <v>installation_region</v>
-      </c>
-      <c r="C22" t="str" s="185"/>
+        <v>glass</v>
+      </c>
+      <c r="C22" t="str" s="185">
+        <v>glass_category,installation_region,window_type</v>
+      </c>
       <c r="D22" t="str" s="185">
-        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
+        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E22" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1690,19 +1692,19 @@
         <v>フロー</v>
       </c>
       <c r="B23" t="str" s="185">
-        <v>glass_category</v>
+        <v>glass_gas</v>
       </c>
       <c r="C23" t="str" s="185">
-        <v>window_type</v>
+        <v>glass_category,window_type</v>
       </c>
       <c r="D23" t="str" s="185">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E23" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1710,19 +1712,19 @@
         <v>フロー</v>
       </c>
       <c r="B24" t="str" s="185">
-        <v>glass</v>
+        <v>glass_spacer</v>
       </c>
       <c r="C24" t="str" s="185">
-        <v>glass_category,installation_region,window_type</v>
+        <v>glass_category,glass_gas,window_type</v>
       </c>
       <c r="D24" t="str" s="185">
-        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E24" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1730,19 +1732,19 @@
         <v>フロー</v>
       </c>
       <c r="B25" t="str" s="185">
-        <v>glass_gas</v>
+        <v>glass_function</v>
       </c>
       <c r="C25" t="str" s="185">
-        <v>glass_category,window_type</v>
+        <v>glass_category,glass,window_type</v>
       </c>
       <c r="D25" t="str" s="185">
-        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E25" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1750,19 +1752,19 @@
         <v>フロー</v>
       </c>
       <c r="B26" t="str" s="185">
-        <v>glass_spacer</v>
+        <v>glass_appearance</v>
       </c>
       <c r="C26" t="str" s="185">
-        <v>glass_category,glass_gas,window_type</v>
+        <v>glass,glass_function</v>
       </c>
       <c r="D26" t="str" s="185">
-        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E26" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1770,19 +1772,17 @@
         <v>フロー</v>
       </c>
       <c r="B27" t="str" s="185">
-        <v>glass_function</v>
-      </c>
-      <c r="C27" t="str" s="185">
-        <v>glass_category,glass,window_type</v>
-      </c>
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C27" t="str" s="185"/>
       <c r="D27" t="str" s="185">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
       </c>
       <c r="E27" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1790,19 +1790,19 @@
         <v>フロー</v>
       </c>
       <c r="B28" t="str" s="185">
-        <v>glass_appearance</v>
+        <v>exterior_cover_type</v>
       </c>
       <c r="C28" t="str" s="185">
-        <v>glass,glass_function</v>
+        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
       </c>
       <c r="D28" t="str" s="185">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
       </c>
       <c r="E28" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1810,17 +1810,19 @@
         <v>フロー</v>
       </c>
       <c r="B29" t="str" s="185">
-        <v>interior_cover_type</v>
-      </c>
-      <c r="C29" t="str" s="185"/>
+        <v>installation_method</v>
+      </c>
+      <c r="C29" t="str" s="185">
+        <v>window_type</v>
+      </c>
       <c r="D29" t="str" s="185">
-        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "内はめ仕様", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E29" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1828,19 +1830,19 @@
         <v>フロー</v>
       </c>
       <c r="B30" t="str" s="185">
-        <v>exterior_cover_type</v>
+        <v>inner_fit_required_component</v>
       </c>
       <c r="C30" t="str" s="185">
-        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+        <v>installation_method</v>
       </c>
       <c r="D30" t="str" s="185">
-        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E30" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1848,17 +1850,17 @@
         <v>フロー</v>
       </c>
       <c r="B31" t="str" s="185">
-        <v>survey_cover_top</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C31" t="str" s="185"/>
       <c r="D31" t="str" s="185">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "入力する寸法", "group": "size", "internal": false}</v>
       </c>
       <c r="E31" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1866,17 +1868,19 @@
         <v>フロー</v>
       </c>
       <c r="B32" t="str" s="185">
-        <v>survey_cover_bottom</v>
-      </c>
-      <c r="C32" t="str" s="185"/>
+        <v>survey_width</v>
+      </c>
+      <c r="C32" t="str" s="185">
+        <v>dimension_basis</v>
+      </c>
       <c r="D32" t="str" s="185">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "採寸幅 WS（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E32" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1884,17 +1888,59 @@
         <v>フロー</v>
       </c>
       <c r="B33" t="str" s="185">
-        <v>survey_cover_side</v>
-      </c>
-      <c r="C33" t="str" s="185"/>
+        <v>survey_height</v>
+      </c>
+      <c r="C33" t="str" s="185">
+        <v>dimension_basis</v>
+      </c>
       <c r="D33" t="str" s="185">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "採寸高さ HS（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E33" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B34" t="str">
+        <v>custom_width</v>
+      </c>
+      <c r="C34" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D34" t="str">
+        <v>{"label": "製品仕上がり幅 WD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E34" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F34" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B35" t="str">
+        <v>custom_height</v>
+      </c>
+      <c r="C35" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D35" t="str">
+        <v>{"label": "製品仕上がり高さ HD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E35" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F35" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -1918,7 +1964,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="178" t="str">
+      <c r="A1" t="str" s="178">
         <v>90_Evidence｜TWタイプ 根拠管理</v>
       </c>
       <c r="B1" s="178"/>
@@ -1931,7 +1977,7 @@
       <c r="I1" s="178"/>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="179" t="str">
+      <c r="A2" t="str" s="179">
         <v>確定値はTW-EVを保持。資料間差異もEvidenceとして記録し、推測で統合しない。</v>
       </c>
       <c r="B2" s="179"/>
@@ -1943,657 +1989,596 @@
       <c r="H2" s="179"/>
       <c r="I2" s="179"/>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="181" t="str">
+      <c r="A4" t="str" s="181">
         <v>evidence_id</v>
       </c>
-      <c r="B4" s="182" t="str">
+      <c r="B4" t="str" s="182">
         <v>情報源種別</v>
       </c>
-      <c r="C4" s="182" t="str">
+      <c r="C4" t="str" s="182">
         <v>資料名</v>
       </c>
-      <c r="D4" s="182" t="str">
+      <c r="D4" t="str" s="182">
         <v>発行年月</v>
       </c>
-      <c r="E4" s="182" t="str">
+      <c r="E4" t="str" s="182">
         <v>ページ/箇所</v>
       </c>
-      <c r="F4" s="182" t="str">
+      <c r="F4" t="str" s="182">
         <v>URL</v>
       </c>
-      <c r="G4" s="182" t="str">
+      <c r="G4" t="str" s="182">
         <v>確認日</v>
       </c>
-      <c r="H4" s="182" t="str">
+      <c r="H4" t="str" s="182">
         <v>確度</v>
       </c>
-      <c r="I4" s="183" t="str">
+      <c r="I4" t="str" s="183">
         <v>根拠内容</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="184" t="str">
+      <c r="A5" t="str" s="184">
         <v>TW-EV-001</v>
       </c>
-      <c r="B5" s="185" t="str">
+      <c r="B5" t="str" s="185">
         <v>共通仕様</v>
       </c>
-      <c r="C5" s="185" t="str">
+      <c r="C5" t="str" s="185">
         <v>サッシ商品マスター共通仕様書_v0.1</v>
       </c>
-      <c r="D5" s="185" t="str">
+      <c r="D5" t="str" s="185">
         <v>2026-08-30更新</v>
       </c>
-      <c r="E5" s="185" t="str">
+      <c r="E5" t="str" s="185">
         <v>§31-34ほか</v>
       </c>
-      <c r="F5" s="185" t="str">
+      <c r="F5" t="str" s="185">
         <v>https://docs.google.com/document/d/1MfixkbV1cZ__DtBknEKsix_nnrXQqjc-LZtXUHwJv_A/edit</v>
       </c>
-      <c r="G5" s="185" t="str">
+      <c r="G5" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H5" s="185" t="str">
+      <c r="H5" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I5" s="186" t="str">
+      <c r="I5" t="str" s="186">
         <v>条件判定、耐風圧特殊案件、OP依存、固有仕様の数値条件</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="184" t="str">
+      <c r="A6" t="str" s="184">
         <v>TW-EV-002</v>
       </c>
-      <c r="B6" s="185" t="str">
+      <c r="B6" t="str" s="185">
         <v>業務用資料集</v>
       </c>
-      <c r="C6" s="185" t="str">
+      <c r="C6" t="str" s="185">
         <v>リプラス・リプラスマンション用 取替窓 業務用資料集</v>
       </c>
-      <c r="D6" s="185" t="str">
+      <c r="D6" t="str" s="185">
         <v>2026-04</v>
       </c>
-      <c r="E6" s="185" t="str">
+      <c r="E6" t="str" s="185">
         <v>目次/居室仕様TWタイプ完成品価格表</v>
       </c>
-      <c r="F6" s="185" t="str">
+      <c r="F6" t="str" s="185">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G6" s="185" t="str">
+      <c r="G6" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H6" s="185" t="str">
+      <c r="H6" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I6" s="186" t="str">
+      <c r="I6" t="str" s="186">
         <v>TWタイプ=引違い窓、構成、価格表・部材構成</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="184" t="str">
+      <c r="A7" t="str" s="184">
         <v>TW-EV-003</v>
       </c>
-      <c r="B7" s="185" t="str">
+      <c r="B7" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C7" s="185" t="str">
+      <c r="C7" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D7" s="185" t="str">
+      <c r="D7" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E7" s="185" t="str">
+      <c r="E7" t="str" s="185">
         <v>p.27</v>
       </c>
-      <c r="F7" s="185" t="str">
+      <c r="F7" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G7" s="185" t="str">
+      <c r="G7" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H7" s="185" t="str">
+      <c r="H7" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I7" s="186" t="str">
+      <c r="I7" t="str" s="186">
         <v>TWタイプ商品体系・色・引違い窓</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="184" t="str">
+      <c r="A8" t="str" s="184">
         <v>TW-EV-004</v>
       </c>
-      <c r="B8" s="185" t="str">
+      <c r="B8" t="str" s="185">
         <v>公式Web</v>
       </c>
-      <c r="C8" s="185" t="str">
+      <c r="C8" t="str" s="185">
         <v>LIXIL リプラス 居室仕様 TWタイプ</v>
       </c>
-      <c r="D8" s="185" t="str">
+      <c r="D8" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E8" s="185" t="str">
+      <c r="E8" t="str" s="185">
         <v>品種/色/ガラス/網戸</v>
       </c>
-      <c r="F8" s="185" t="str">
+      <c r="F8" t="str" s="185">
         <v>https://www.lixil.co.jp/lineup/window/replus/variation/tw-type/</v>
       </c>
-      <c r="G8" s="185" t="str">
+      <c r="G8" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H8" s="185" t="str">
+      <c r="H8" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I8" s="186" t="str">
+      <c r="I8" t="str" s="186">
         <v>現行Webで引違い窓、色5×5、主要Low-E構成、ネット4種</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="184" t="str">
+      <c r="A9" t="str" s="184">
         <v>TW-EV-005</v>
       </c>
-      <c r="B9" s="185" t="str">
+      <c r="B9" t="str" s="185">
         <v>業務用資料集</v>
       </c>
-      <c r="C9" s="185" t="str">
+      <c r="C9" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D9" s="185" t="str">
+      <c r="D9" t="str" s="185">
         <v>2026-04</v>
       </c>
-      <c r="E9" s="185" t="str">
+      <c r="E9" t="str" s="185">
         <v>p.4-7相当</v>
       </c>
-      <c r="F9" s="185" t="str">
+      <c r="F9" t="str" s="185">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G9" s="185" t="str">
+      <c r="G9" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H9" s="185" t="str">
+      <c r="H9" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I9" s="186" t="str">
+      <c r="I9" t="str" s="186">
         <v>TG/把手/大壁和室用、2/4枚建、採寸/出来寸、ガス、網戸</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="184" t="str">
+      <c r="A10" t="str" s="184">
         <v>TW-EV-006</v>
       </c>
-      <c r="B10" s="185" t="str">
+      <c r="B10" t="str" s="185">
         <v>業務用資料集</v>
       </c>
-      <c r="C10" s="185" t="str">
+      <c r="C10" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D10" s="185" t="str">
+      <c r="D10" t="str" s="185">
         <v>2026-04</v>
       </c>
-      <c r="E10" s="185" t="str">
+      <c r="E10" t="str" s="185">
         <v>TWタイプ部材構成図/網戸注記</v>
       </c>
-      <c r="F10" s="185" t="str">
+      <c r="F10" t="str" s="185">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G10" s="185" t="str">
+      <c r="G10" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H10" s="185" t="str">
+      <c r="H10" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I10" s="186" t="str">
+      <c r="I10" t="str" s="186">
         <v>中桟付網戸 1648≤HD≤2405、内嵌め時既設上枠ベース材</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="184" t="str">
+      <c r="A11" t="str" s="184">
         <v>TW-EV-007</v>
       </c>
-      <c r="B11" s="185" t="str">
+      <c r="B11" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C11" s="185" t="str">
+      <c r="C11" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D11" s="185" t="str">
+      <c r="D11" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E11" s="185" t="str">
+      <c r="E11" t="str" s="185">
         <v>p.96</v>
       </c>
-      <c r="F11" s="185" t="str">
+      <c r="F11" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G11" s="185" t="str">
+      <c r="G11" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H11" s="185" t="str">
+      <c r="H11" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I11" s="186" t="str">
+      <c r="I11" t="str" s="186">
         <v>TWタイプ寸法特注範囲・境界式・耐風圧/ガラス制限注記</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="184" t="str">
+      <c r="A12" t="str" s="184">
         <v>TW-EV-008</v>
       </c>
-      <c r="B12" s="185" t="str">
+      <c r="B12" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C12" s="185" t="str">
+      <c r="C12" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D12" s="185" t="str">
+      <c r="D12" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E12" s="185" t="str">
+      <c r="E12" t="str" s="185">
         <v>p.56</v>
       </c>
-      <c r="F12" s="185" t="str">
+      <c r="F12" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G12" s="185" t="str">
+      <c r="G12" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H12" s="185" t="str">
+      <c r="H12" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I12" s="186" t="str">
+      <c r="I12" t="str" s="186">
         <v>専用Low-Eトリプル、Low-E構成、アルゴン/クリプトン、樹脂スペーサー、追加機能</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="184" t="str">
+      <c r="A13" t="str" s="184">
         <v>TW-EV-009</v>
       </c>
-      <c r="B13" s="185" t="str">
+      <c r="B13" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C13" s="185" t="str">
+      <c r="C13" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D13" s="185" t="str">
+      <c r="D13" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E13" s="185" t="str">
+      <c r="E13" t="str" s="185">
         <v>p.124</v>
       </c>
-      <c r="F13" s="185" t="str">
+      <c r="F13" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G13" s="185" t="str">
+      <c r="G13" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H13" s="185" t="str">
+      <c r="H13" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I13" s="186" t="str">
+      <c r="I13" t="str" s="186">
         <v>有償品取付可否、TW非適用OP、共通既設窓可否</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="184" t="str">
+      <c r="A14" t="str" s="184">
         <v>TW-EV-010</v>
       </c>
-      <c r="B14" s="185" t="str">
+      <c r="B14" t="str" s="185">
         <v>業務用資料集</v>
       </c>
-      <c r="C14" s="185" t="str">
+      <c r="C14" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D14" s="185" t="str">
+      <c r="D14" t="str" s="185">
         <v>2026-04</v>
       </c>
-      <c r="E14" s="185" t="str">
+      <c r="E14" t="str" s="185">
         <v>TWタイプ有償品</v>
       </c>
-      <c r="F14" s="185" t="str">
+      <c r="F14" t="str" s="185">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G14" s="185" t="str">
+      <c r="G14" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H14" s="185" t="str">
+      <c r="H14" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I14" s="186" t="str">
+      <c r="I14" t="str" s="186">
         <v>小開口ストッパー70/110、専用クレセント、4枚建不可、スマートクレセント併用不可</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="184" t="str">
+      <c r="A15" t="str" s="184">
         <v>TW-EV-011</v>
       </c>
-      <c r="B15" s="185" t="str">
+      <c r="B15" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C15" s="185" t="str">
+      <c r="C15" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D15" s="185" t="str">
+      <c r="D15" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E15" s="185" t="str">
+      <c r="E15" t="str" s="185">
         <v>p.227</v>
       </c>
-      <c r="F15" s="185" t="str">
+      <c r="F15" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G15" s="185" t="str">
+      <c r="G15" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H15" s="185" t="str">
+      <c r="H15" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I15" s="186" t="str">
+      <c r="I15" t="str" s="186">
         <v>TW専用現調/発注シート：採寸、見付、枠見込み、施工区分、色、網戸、OP</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="184" t="str">
+      <c r="A16" t="str" s="184">
         <v>TW-EV-012</v>
       </c>
-      <c r="B16" s="185" t="str">
+      <c r="B16" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C16" s="185" t="str">
+      <c r="C16" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E16" s="185" t="str">
+      <c r="E16" t="str" s="185">
         <v>ガラス面積/戸車耐荷重表</v>
       </c>
-      <c r="F16" s="185" t="str">
+      <c r="F16" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G16" s="185" t="str">
+      <c r="G16" t="str" s="185">
         <v>2026-08-30</v>
       </c>
-      <c r="H16" s="185" t="str">
+      <c r="H16" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I16" s="186" t="str">
+      <c r="I16" t="str" s="186">
         <v>ガラス構成により製作不可となる特殊境界</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="187" t="str">
+      <c r="A17" t="str" s="187">
         <v>TW-EV-013</v>
       </c>
-      <c r="B17" s="188" t="str">
+      <c r="B17" t="str" s="188">
         <v>Evidence差異</v>
       </c>
-      <c r="C17" s="188" t="str">
+      <c r="C17" t="str" s="188">
         <v>商品体系p.56・現行Web vs 現調/発注p.227</v>
       </c>
-      <c r="D17" s="188" t="str">
+      <c r="D17" t="str" s="188">
         <v>2025-08/現行</v>
       </c>
-      <c r="E17" s="188" t="str">
+      <c r="E17" t="str" s="188">
         <v>Low-E構成</v>
       </c>
-      <c r="F17" s="188" t="str">
+      <c r="F17" t="str" s="188">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G17" s="188" t="str">
+      <c r="G17" t="str" s="188">
         <v>2026-08-30</v>
       </c>
-      <c r="H17" s="188" t="str">
+      <c r="H17" t="str" s="188">
         <v>REVIEW</v>
       </c>
-      <c r="I17" s="189" t="str">
+      <c r="I17" t="str" s="189">
         <v>p.227にグリーン×クリア記載、一方p.56/現行WebのTW主要構成に未掲載。通常UIでは非表示とする。</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>DELTA-KEY-EV-V4</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E18" s="36" t="inlineStr">
-        <is>
-          <t>PDF 3,44,49</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H18" s="36" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>ADD_OPTION_AND_DENY_COMBINATION / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A18" t="str" s="35">
+        <v>DELTA-KEY-EV-V4</v>
+      </c>
+      <c r="B18" t="str" s="36">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C18" t="str" s="36">
+        <v>IS9800</v>
+      </c>
+      <c r="D18" t="str" s="36">
+        <v>2026-10</v>
+      </c>
+      <c r="E18" t="str" s="36">
+        <v>PDF 3,44,49</v>
+      </c>
+      <c r="F18" t="str" s="36">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G18" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H18" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I18" t="str" s="37">
+        <v>ADD_OPTION_AND_DENY_COMBINATION / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>DELTA-SPACER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E19" s="36" t="inlineStr">
-        <is>
-          <t>PDF 52,104,116,120</t>
-        </is>
-      </c>
-      <c r="F19" s="36" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G19" s="36" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H19" s="36" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I19" s="37" t="inlineStr">
-        <is>
-          <t>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A19" t="str" s="35">
+        <v>DELTA-SPACER-EV-V4</v>
+      </c>
+      <c r="B19" t="str" s="36">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C19" t="str" s="36">
+        <v>IS9800</v>
+      </c>
+      <c r="D19" t="str" s="36">
+        <v>2026-10</v>
+      </c>
+      <c r="E19" t="str" s="36">
+        <v>PDF 52,104,116,120</v>
+      </c>
+      <c r="F19" t="str" s="36">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G19" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H19" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I19" t="str" s="37">
+        <v>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>DELTA-CASING-EV-V4</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H20" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I20" s="40" t="inlineStr">
-        <is>
-          <t>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A20" t="str" s="38">
+        <v>DELTA-CASING-EV-V4</v>
+      </c>
+      <c r="B20" t="str" s="39">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C20" t="str" s="39">
+        <v>IS9800</v>
+      </c>
+      <c r="D20" t="str" s="39">
+        <v>2026-10</v>
+      </c>
+      <c r="E20" t="str" s="39">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F20" t="str" s="39">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G20" t="str" s="39">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H20" t="str" s="39">
+        <v>HIGH</v>
+      </c>
+      <c r="I20" t="str" s="40">
+        <v>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-FILLER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="inlineStr">
-        <is>
-          <t>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A21" t="str" s="28">
+        <v>DELTA-FILLER-EV-V4</v>
+      </c>
+      <c r="B21" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C21" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D21" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E21" t="str" s="28">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F21" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G21" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H21" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I21" t="str" s="28">
+        <v>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-LEADTIME-EV-V4</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>PDF 235</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I22" s="28" t="inlineStr">
-        <is>
-          <t>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A22" t="str" s="28">
+        <v>DELTA-LEADTIME-EV-V4</v>
+      </c>
+      <c r="B22" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C22" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D22" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E22" t="str" s="28">
+        <v>PDF 235</v>
+      </c>
+      <c r="F22" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G22" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H22" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I22" t="str" s="28">
+        <v>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
+      <c r="A23" t="str" s="28">
+        <v>EV-DIMENSIONS-INNER-FIT-V11</v>
+      </c>
+      <c r="B23" t="str" s="28">
+        <v>公式商品カタログ</v>
+      </c>
+      <c r="C23" t="str" s="28">
+        <v>リプラス SN1200</v>
+      </c>
+      <c r="D23" t="str" s="28">
+        <v>2025-08</v>
+      </c>
+      <c r="E23" t="str" s="28">
+        <v>PDF252/254・231/233/247/249/251</v>
+      </c>
+      <c r="F23" t="str" s="28">
+        <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
+      </c>
+      <c r="G23" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H23" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I23" t="str" s="28">
+        <v>採寸/出来寸の相互換算と標準/内はめの施工仕様を共通Runtimeへ接続</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="28"/>
@@ -10947,7 +10932,7 @@
         <v>リプラス住宅用 → 仕様</v>
       </c>
       <c r="E4" t="str" s="186">
-        <v>今回承認されたアプリ運用ルール</v>
+        <v>アプリ運用ルール</v>
       </c>
       <c r="F4"/>
     </row>
@@ -11046,16 +11031,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="185">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>内はめ仕様</v>
       </c>
       <c r="C10" t="str" s="185">
-        <v>interior_finish</v>
+        <v>inner_fit</v>
       </c>
       <c r="D10" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>ガラスの後で選択</v>
       </c>
       <c r="F10"/>
     </row>
@@ -11064,16 +11049,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="str" s="185">
-        <v>室外側の仕上げ・化粧カバー</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C11" t="str" s="185">
-        <v>exterior_finish</v>
+        <v>interior_finish</v>
       </c>
       <c r="D11" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E11" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F11"/>
     </row>
@@ -11082,10 +11067,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="185">
-        <v>追加部材・オプション</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C12" t="str" s="185">
-        <v>options</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D12" t="str" s="185">
         <v>選択・確認</v>
@@ -11100,10 +11085,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="185">
-        <v>選択した部材の仕様</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C13" t="str" s="185">
-        <v>part_detail</v>
+        <v>options</v>
       </c>
       <c r="D13" t="str" s="185">
         <v>選択・確認</v>
@@ -11118,25 +11103,35 @@
         <v>11</v>
       </c>
       <c r="B14" t="str" s="185">
-        <v>製品寸法</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C14" t="str" s="185">
-        <v>size</v>
+        <v>part_detail</v>
       </c>
       <c r="D14" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E14" t="str" s="186">
-        <v>採寸後に再評価</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" s="184"/>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="185"/>
-      <c r="E15" s="186"/>
+      <c r="A15" t="n" s="184">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>製品寸法</v>
+      </c>
+      <c r="C15" t="str" s="185">
+        <v>size</v>
+      </c>
+      <c r="D15" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>採寸と仕上がりを併記</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16">

--- a/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
@@ -1316,7 +1316,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1336,7 +1336,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1354,7 +1354,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1368,13 +1368,13 @@
         <v>installation_method</v>
       </c>
       <c r="D6" t="str" s="185">
-        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "TW-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "TW-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "TW-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "TW-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。", "resolvedNoticeVisibility": "INTERNAL_ONLY"}</v>
       </c>
       <c r="E6" t="str" s="186">
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1392,7 +1392,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1412,7 +1412,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1432,7 +1432,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1452,7 +1452,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1472,7 +1472,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1492,7 +1492,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1510,7 +1510,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1528,7 +1528,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1542,13 +1542,13 @@
         <v>sash_exterior_color</v>
       </c>
       <c r="D15" t="str" s="185">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E15" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1566,7 +1566,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1580,13 +1580,13 @@
         <v>sash_interior_color</v>
       </c>
       <c r="D17" t="str" s="185">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E17" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1606,7 +1606,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1626,7 +1626,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1644,7 +1644,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1664,7 +1664,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1684,7 +1684,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1704,7 +1704,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1724,7 +1724,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1744,7 +1744,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1764,7 +1764,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1782,7 +1782,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1802,7 +1802,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1822,7 +1822,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1836,13 +1836,13 @@
         <v>installation_method</v>
       </c>
       <c r="D30" t="str" s="185">
-        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E30" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1860,7 +1860,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1880,7 +1880,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1900,7 +1900,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1920,7 +1920,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1940,7 +1940,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
   </sheetData>

--- a/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_TW.xlsx
@@ -1316,7 +1316,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1336,7 +1336,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1354,7 +1354,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1374,7 +1374,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1392,7 +1392,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1412,7 +1412,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1432,7 +1432,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1452,7 +1452,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1472,7 +1472,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1492,7 +1492,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1510,7 +1510,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1528,7 +1528,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1548,7 +1548,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1566,7 +1566,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1586,7 +1586,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1606,7 +1606,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1626,7 +1626,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1644,7 +1644,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1658,13 +1658,13 @@
         <v>window_type</v>
       </c>
       <c r="D21" t="str" s="185">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false, "rank": 1}</v>
       </c>
       <c r="E21" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1675,16 +1675,16 @@
         <v>glass</v>
       </c>
       <c r="C22" t="str" s="185">
-        <v>glass_category,installation_region,window_type</v>
+        <v>glass_category,glass_appearance,installation_region,window_type</v>
       </c>
       <c r="D22" t="str" s="185">
-        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
+        <v>{"label": "Low-E構成", "group": "glazing", "internal": false, "rank": 3}</v>
       </c>
       <c r="E22" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1704,7 +1704,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1724,7 +1724,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1735,16 +1735,16 @@
         <v>glass_function</v>
       </c>
       <c r="C25" t="str" s="185">
-        <v>glass_category,glass,window_type</v>
+        <v>glass_category,glass_appearance,glass,window_type</v>
       </c>
       <c r="D25" t="str" s="185">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false, "rank": 4}</v>
       </c>
       <c r="E25" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1755,16 +1755,16 @@
         <v>glass_appearance</v>
       </c>
       <c r="C26" t="str" s="185">
-        <v>glass,glass_function</v>
+        <v>glass_category</v>
       </c>
       <c r="D26" t="str" s="185">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種", "group": "glazing", "internal": false, "rank": 2}</v>
       </c>
       <c r="E26" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1782,7 +1782,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1802,7 +1802,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1822,7 +1822,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1842,7 +1842,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1860,7 +1860,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1880,7 +1880,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1900,7 +1900,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1920,7 +1920,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1940,7 +1940,67 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B36" t="str">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C36" t="str">
+        <v>glass_category</v>
+      </c>
+      <c r="D36" t="str">
+        <v>{"key": "glass_appearance", "displayLabel": "ガラス種", "dataType": "ENUM", "displayOrder": 710, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category"], "selector": {"glass_category": {"$exists": true}}, "choices": [{"value": "MILKY", "displayLabel": "乳白", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "CLEAR", "displayLabel": "透明", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 1}, {"value": "OBSCURE", "displayLabel": "型板", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "FROST", "displayLabel": "フロスト", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}]}</v>
+      </c>
+      <c r="E36" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F36" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B37" t="str">
+        <v>glass</v>
+      </c>
+      <c r="C37" t="str">
+        <v>glass_category,glass_appearance,installation_region,window_type</v>
+      </c>
+      <c r="D37" t="str">
+        <v>{"key": "glass", "displayLabel": "Low-E構成", "dataType": "ENUM", "displayOrder": 720, "choices": [{"value": "TW-GL-CC", "displayLabel": "クリア×クリア", "evidenceIds": ["TW-EV-004,008"], "selector": {"window_type": "RPL_TW_SLD", "glass_category": "TW-GL-TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "TW-GL-GG", "displayLabel": "グリーン×グリーン", "evidenceIds": ["TW-EV-004,008"], "selector": {"window_type": "RPL_TW_SLD", "glass_category": "TW-GL-TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "TW-GL-CG", "displayLabel": "クリア×グリーン", "evidenceIds": ["TW-EV-004,008"], "selector": {"window_type": "RPL_TW_SLD", "glass_category": "TW-GL-TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "TW-GL-CB", "displayLabel": "クリア×ブロンズ", "evidenceIds": ["TW-EV-008"], "selector": {"window_type": "RPL_TW_SLD", "glass_category": "TW-GL-TRIPLE", "installation_region": {"$in": ["北海道", "東北"]}}, "metadata": {"manualCheck": true}}], "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "installation_region", "window_type"], "selector": {"glass_category": {"$exists": true}}}</v>
+      </c>
+      <c r="E37" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F37" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B38" t="str">
+        <v>glass_function</v>
+      </c>
+      <c r="C38" t="str">
+        <v>glass_category,glass_appearance,glass,window_type</v>
+      </c>
+      <c r="D38" t="str">
+        <v>{"key": "glass_function", "displayLabel": "ガラス追加機能", "dataType": "ENUM", "displayOrder": 730, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "glass", "window_type"], "selector": {"glass": {"$exists": true}}, "choices": [{"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "TW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "TW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "TW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "TW-GL-TRIPLE", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "THIN", "displayLabel": "特殊薄板合わせ", "selector": {"all": [{"glass_category": "TW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 5}]}</v>
+      </c>
+      <c r="E38" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
   </sheetData>
